--- a/artfynd/A 684-2023 artfynd.xlsx
+++ b/artfynd/A 684-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 684-2023 artfynd.xlsx
+++ b/artfynd/A 684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1976269</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758184.9864815362</v>
+        <v>758185</v>
       </c>
       <c r="R2" t="n">
-        <v>7108882.130833967</v>
+        <v>7108882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2010-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>107525939</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758100.9877781421</v>
+        <v>758101</v>
       </c>
       <c r="R3" t="n">
-        <v>7108879.112174971</v>
+        <v>7108879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -922,37 +902,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107525964</v>
+        <v>106644147</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,10 +936,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -974,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758214</v>
+        <v>758191</v>
       </c>
       <c r="R4" t="n">
-        <v>7109058</v>
+        <v>7108958</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,27 +983,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tyst förbiflygning</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,56 +1018,55 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Bo Leijon</t>
+          <t>Via Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107526049</v>
+        <v>106644157</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1103,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758534.1879936529</v>
+        <v>758253</v>
       </c>
       <c r="R5" t="n">
-        <v>7109270.641953911</v>
+        <v>7108574</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1106,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1141,244 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Via Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107525980</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brattåker, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>758554</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7109039</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Roger Olofsson, Bo Leijon</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107526049</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brattåker, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>758534</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7109271</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Bo Leijon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 684-2023 artfynd.xlsx
+++ b/artfynd/A 684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976269</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107525939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106644147</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106644157</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107525980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,8 +1409,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107526049</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>